--- a/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{601442DE-EA94-4582-865B-37E8E5F8278D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2820058D-F927-495A-838D-2729ED7FBB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3503,7 +3503,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{933254C0-AB4D-4F17-97A9-CC2A2D03D0E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF8AC84-46FB-45D7-95D9-75C882B4AE5D}">
   <dimension ref="B2:AJ419"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11654,7 +11654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B808DA0-DB55-4DF0-832B-B55BA6CF7721}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450C7390-4DDB-4691-B911-D850CE58C87A}">
   <dimension ref="B9:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A5805F3-FC2C-48AE-B781-69DDAE240800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC6FFD6-65FD-41EF-B390-B0E06F220579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3456" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="709">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2257,15 +2257,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -3465,10 +3456,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD77D081-F788-4FE3-9D65-8AE7D213A4FF}">
-  <dimension ref="B2:AJ419"/>
+  <dimension ref="B2:AF419"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -3481,11 +3472,8 @@
       <c r="U2" t="s">
         <v>239</v>
       </c>
-      <c r="AH2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -3537,17 +3525,8 @@
       <c r="AA3" t="s">
         <v>189</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>190</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>120</v>
       </c>
@@ -3614,17 +3593,8 @@
       <c r="AF4" t="s">
         <v>706</v>
       </c>
-      <c r="AH4" t="s">
-        <v>709</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>710</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>121</v>
       </c>
@@ -3688,17 +3658,8 @@
       <c r="AF5" t="s">
         <v>707</v>
       </c>
-      <c r="AH5" t="s">
-        <v>711</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>710</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>122</v>
       </c>
@@ -3763,7 +3724,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>123</v>
       </c>
@@ -3813,7 +3774,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>124</v>
       </c>
@@ -3863,7 +3824,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>125</v>
       </c>
@@ -3913,7 +3874,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>126</v>
       </c>
@@ -3963,7 +3924,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>127</v>
       </c>
@@ -4013,7 +3974,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>128</v>
       </c>
@@ -4063,7 +4024,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>129</v>
       </c>
@@ -4113,7 +4074,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>130</v>
       </c>
@@ -4163,7 +4124,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>131</v>
       </c>
@@ -4213,7 +4174,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>132</v>
       </c>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC6FFD6-65FD-41EF-B390-B0E06F220579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7994B8F2-FB6D-4ED9-BC59-315FE9A58DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3456" uniqueCount="712">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2257,6 +2257,15 @@
   </si>
   <si>
     <t>STG</t>
+  </si>
+  <si>
+    <t>Trd_electricity import</t>
+  </si>
+  <si>
+    <t>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</t>
+  </si>
+  <si>
+    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -3455,11 +3464,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD77D081-F788-4FE3-9D65-8AE7D213A4FF}">
-  <dimension ref="B2:AF419"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC192017-8A17-40AE-AC5A-5E0475998BF0}">
+  <dimension ref="B2:AJ419"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -3472,8 +3481,11 @@
       <c r="U2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -3525,8 +3537,17 @@
       <c r="AA3" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>190</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>120</v>
       </c>
@@ -3593,8 +3614,17 @@
       <c r="AF4" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH4" t="s">
+        <v>709</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>710</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>121</v>
       </c>
@@ -3658,8 +3688,17 @@
       <c r="AF5" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AH5" t="s">
+        <v>711</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>710</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>122</v>
       </c>
@@ -3724,7 +3763,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>123</v>
       </c>
@@ -3774,7 +3813,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>124</v>
       </c>
@@ -3824,7 +3863,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>125</v>
       </c>
@@ -3874,7 +3913,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>126</v>
       </c>
@@ -3924,7 +3963,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>127</v>
       </c>
@@ -3974,7 +4013,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>128</v>
       </c>
@@ -4024,7 +4063,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>129</v>
       </c>
@@ -4074,7 +4113,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>130</v>
       </c>
@@ -4124,7 +4163,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>131</v>
       </c>
@@ -4174,7 +4213,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>132</v>
       </c>
@@ -11288,7 +11327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D3DCBB-F40A-43F8-8364-852EF00C2AE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17DCAE2-3AA6-42A1-AE78-27C43F9B5535}">
   <dimension ref="B9:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7994B8F2-FB6D-4ED9-BC59-315FE9A58DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEA8BF07-1112-41DD-B29C-029232459839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3456" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="709">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2257,15 +2257,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_NG10-330,e_w559542338-330,e_w669957212-330,e_w706082453-330,e_w746582404-330</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -3464,11 +3455,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC192017-8A17-40AE-AC5A-5E0475998BF0}">
-  <dimension ref="B2:AJ419"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3991000C-5A2D-48B7-8F3E-7016AD8983DB}">
+  <dimension ref="B2:AF419"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -3481,11 +3472,8 @@
       <c r="U2" t="s">
         <v>239</v>
       </c>
-      <c r="AH2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -3537,17 +3525,8 @@
       <c r="AA3" t="s">
         <v>189</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>190</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>120</v>
       </c>
@@ -3614,17 +3593,8 @@
       <c r="AF4" t="s">
         <v>706</v>
       </c>
-      <c r="AH4" t="s">
-        <v>709</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>710</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>121</v>
       </c>
@@ -3688,17 +3658,8 @@
       <c r="AF5" t="s">
         <v>707</v>
       </c>
-      <c r="AH5" t="s">
-        <v>711</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>710</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>122</v>
       </c>
@@ -3763,7 +3724,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>123</v>
       </c>
@@ -3813,7 +3774,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>124</v>
       </c>
@@ -3863,7 +3824,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>125</v>
       </c>
@@ -3913,7 +3874,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>126</v>
       </c>
@@ -3963,7 +3924,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>127</v>
       </c>
@@ -4013,7 +3974,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>128</v>
       </c>
@@ -4063,7 +4024,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>129</v>
       </c>
@@ -4113,7 +4074,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>130</v>
       </c>
@@ -4163,7 +4124,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>131</v>
       </c>
@@ -4213,7 +4174,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>132</v>
       </c>
@@ -11327,7 +11288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17DCAE2-3AA6-42A1-AE78-27C43F9B5535}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C682E0-A90F-4DAB-910E-ACFF2D44FFF8}">
   <dimension ref="B9:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D826AAF9-C85E-46EA-B9E6-F5310381C29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5016227-A702-4941-83A2-2DEEA07EB06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2751,7 +2751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B12C487-6E1F-4432-9A7C-6D8F26929CC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{770FDC55-A7CA-4CFB-BE2E-CAADF0F535AC}">
   <dimension ref="B2:AF419"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10584,7 +10584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D283CF73-D00C-4862-91F1-108E3F6EAD91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F626B2D0-FF30-48F7-9781-1EAE66C98145}">
   <dimension ref="B9:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
